--- a/Results/Comparison - Valence.xlsx
+++ b/Results/Comparison - Valence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikoo\Desktop\Thesis\Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67F5FB2-A9BD-4806-8184-63EA49C4C323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0DB3BE-3D93-449F-800B-DEE20A9FCDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8D592C9F-CC51-43DD-B2E3-0BF015735963}"/>
   </bookViews>
@@ -400,9 +400,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -410,6 +407,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -437,10 +450,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -459,16 +468,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -862,28 +862,28 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>0.57707641196013204</v>
+        <v>0.57880214101144301</v>
       </c>
       <c r="E2">
-        <v>0.143981055197692</v>
+        <v>0.184896081378817</v>
       </c>
       <c r="F2">
-        <v>0.69738259156863802</v>
+        <v>0.64873240454635805</v>
       </c>
       <c r="G2">
-        <v>0.11378088069947299</v>
+        <v>0.16764824735817199</v>
       </c>
       <c r="H2">
-        <v>0.58713547434477598</v>
+        <v>0.60279623477297795</v>
       </c>
       <c r="I2">
-        <v>0.158393173864118</v>
+        <v>0.17348987653307299</v>
       </c>
       <c r="J2">
-        <v>0.91373200442967795</v>
+        <v>0.75011074197120697</v>
       </c>
       <c r="K2">
-        <v>0.13003234359403601</v>
+        <v>0.21940420292951601</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -897,28 +897,28 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>0.58433001107419702</v>
+        <v>0.58142303433001097</v>
       </c>
       <c r="E3">
-        <v>0.15434972636935401</v>
+        <v>0.16217321203413301</v>
       </c>
       <c r="F3">
-        <v>0.65576077669100896</v>
+        <v>0.64859249277853903</v>
       </c>
       <c r="G3">
-        <v>0.143085431856566</v>
+        <v>0.154286936902232</v>
       </c>
       <c r="H3">
-        <v>0.614811738648947</v>
+        <v>0.60647840531561403</v>
       </c>
       <c r="I3">
-        <v>0.171132677746722</v>
+        <v>0.177386675627971</v>
       </c>
       <c r="J3">
-        <v>0.75315614617940196</v>
+        <v>0.74584717607973405</v>
       </c>
       <c r="K3">
-        <v>0.200948104042907</v>
+        <v>0.21277435086303401</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -932,28 +932,28 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0.53001107419712001</v>
+        <v>0.54032853451458096</v>
       </c>
       <c r="E4">
-        <v>0.15932681380734201</v>
+        <v>0.18203034174753999</v>
       </c>
       <c r="F4">
-        <v>0.61900489691187299</v>
+        <v>0.58345930555232794</v>
       </c>
       <c r="G4">
-        <v>0.154355311008368</v>
+        <v>0.197529954050357</v>
       </c>
       <c r="H4">
-        <v>0.57151162790697596</v>
+        <v>0.57782392026578</v>
       </c>
       <c r="I4">
-        <v>0.180909280316947</v>
+        <v>0.21237148311922499</v>
       </c>
       <c r="J4">
-        <v>0.74972314507198201</v>
+        <v>0.64440753045404198</v>
       </c>
       <c r="K4">
-        <v>0.23933024621149401</v>
+        <v>0.26350607006052701</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -967,28 +967,28 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>0.48564045773348002</v>
+        <v>0.52762089331856699</v>
       </c>
       <c r="E5">
-        <v>0.18989890478486901</v>
+        <v>0.185065800818593</v>
       </c>
       <c r="F5">
-        <v>0.52825094801838901</v>
+        <v>0.56233262861169797</v>
       </c>
       <c r="G5">
-        <v>0.20351469821229601</v>
+        <v>0.187166817096449</v>
       </c>
       <c r="H5">
-        <v>0.54515503875968996</v>
+        <v>0.59033776301218099</v>
       </c>
       <c r="I5">
-        <v>0.22313468796340899</v>
+        <v>0.22651172170790801</v>
       </c>
       <c r="J5">
-        <v>0.57225913621262403</v>
+        <v>0.58466223698781805</v>
       </c>
       <c r="K5">
-        <v>0.27098567142806501</v>
+        <v>0.22877857349854</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1002,28 +1002,28 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>0.59882798080472499</v>
+        <v>0.64935400516795805</v>
       </c>
       <c r="E6">
-        <v>0.15762419136511699</v>
+        <v>0.19200304014744901</v>
       </c>
       <c r="F6">
-        <v>0.69558890721681399</v>
+        <v>0.68801147173240196</v>
       </c>
       <c r="G6">
-        <v>0.139364781242834</v>
+        <v>0.188766106100762</v>
       </c>
       <c r="H6">
-        <v>0.60700442967884805</v>
+        <v>0.68283499446290097</v>
       </c>
       <c r="I6">
-        <v>0.166992485138409</v>
+        <v>0.22071880920838599</v>
       </c>
       <c r="J6">
-        <v>0.864728682170542</v>
+        <v>0.74064230343300097</v>
       </c>
       <c r="K6">
-        <v>0.17541301020934</v>
+        <v>0.231350990822842</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1037,28 +1037,28 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>0.616066814322628</v>
+        <v>0.60734588409006995</v>
       </c>
       <c r="E7">
-        <v>0.18402982800207901</v>
+        <v>0.18610174212209701</v>
       </c>
       <c r="F7">
-        <v>0.68327202513248997</v>
+        <v>0.65419515884632096</v>
       </c>
       <c r="G7">
-        <v>0.17437773661435699</v>
+        <v>0.192281985931196</v>
       </c>
       <c r="H7">
-        <v>0.62755629383536304</v>
+        <v>0.63829826504245102</v>
       </c>
       <c r="I7">
-        <v>0.19851666346567801</v>
+        <v>0.22240917510506</v>
       </c>
       <c r="J7">
-        <v>0.80415282392026499</v>
+        <v>0.73316722037652204</v>
       </c>
       <c r="K7">
-        <v>0.22154856476969001</v>
+        <v>0.24769910716418</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1072,28 +1072,28 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>0.62715946843853798</v>
+        <v>0.64614248800295304</v>
       </c>
       <c r="E8">
-        <v>0.15461252746714799</v>
+        <v>0.185069465263971</v>
       </c>
       <c r="F8">
-        <v>0.66418762116436503</v>
+        <v>0.64314212918864</v>
       </c>
       <c r="G8">
-        <v>0.18287489468927101</v>
+        <v>0.23583168416615399</v>
       </c>
       <c r="H8">
-        <v>0.64784053156146104</v>
+        <v>0.68732004429678795</v>
       </c>
       <c r="I8">
-        <v>0.204654878126136</v>
+        <v>0.249982186218807</v>
       </c>
       <c r="J8">
-        <v>0.73859357696566896</v>
+        <v>0.66982281284606804</v>
       </c>
       <c r="K8">
-        <v>0.24508594347872001</v>
+        <v>0.28703860712679002</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1107,28 +1107,28 @@
         <v>14</v>
       </c>
       <c r="D9">
-        <v>0.533684016242155</v>
+        <v>0.55145810262089301</v>
       </c>
       <c r="E9">
-        <v>0.18852953153482599</v>
+        <v>0.16381952017014201</v>
       </c>
       <c r="F9">
-        <v>0.54803362012664303</v>
+        <v>0.57060136246182702</v>
       </c>
       <c r="G9">
-        <v>0.22748582977148399</v>
+        <v>0.182745478652242</v>
       </c>
       <c r="H9">
-        <v>0.54972314507198194</v>
+        <v>0.592026578073089</v>
       </c>
       <c r="I9">
-        <v>0.23869482052385399</v>
+        <v>0.19782466968748899</v>
       </c>
       <c r="J9">
-        <v>0.57679955703211505</v>
+        <v>0.59883720930232498</v>
       </c>
       <c r="K9">
-        <v>0.26288054058281102</v>
+        <v>0.25529945673057097</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1142,28 +1142,28 @@
         <v>13</v>
       </c>
       <c r="D10">
-        <v>0.63309339239571705</v>
+        <v>0.63471760797342103</v>
       </c>
       <c r="E10">
-        <v>0.17474714565740901</v>
+        <v>0.16399282450064601</v>
       </c>
       <c r="F10">
-        <v>0.68326518442797501</v>
+        <v>0.65577703949796895</v>
       </c>
       <c r="G10">
-        <v>0.17271769493512801</v>
+        <v>0.19880746867004401</v>
       </c>
       <c r="H10">
-        <v>0.648947951273532</v>
+        <v>0.65703211517165006</v>
       </c>
       <c r="I10">
-        <v>0.18658914695819101</v>
+        <v>0.206928551893827</v>
       </c>
       <c r="J10">
-        <v>0.768493909191583</v>
+        <v>0.69928017718715296</v>
       </c>
       <c r="K10">
-        <v>0.22460382906794699</v>
+        <v>0.248888545995436</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1174,31 +1174,31 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>0.58607419712070796</v>
+        <v>0.57141011443336998</v>
       </c>
       <c r="E11">
-        <v>0.126049120152814</v>
+        <v>0.17735655719302101</v>
       </c>
       <c r="F11">
-        <v>0.68201811108787802</v>
+        <v>0.63894774476169802</v>
       </c>
       <c r="G11">
-        <v>0.126355902034096</v>
+        <v>0.19292571494781099</v>
       </c>
       <c r="H11">
-        <v>0.59686231081579899</v>
+        <v>0.59459210040605304</v>
       </c>
       <c r="I11">
-        <v>0.16274364437013999</v>
+        <v>0.22054223482247501</v>
       </c>
       <c r="J11">
-        <v>0.84928017718715398</v>
+        <v>0.74972314507198201</v>
       </c>
       <c r="K11">
-        <v>0.18336140131442499</v>
+        <v>0.24721846020890101</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -1209,31 +1209,31 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>0.57399409376153498</v>
+        <v>0.59063307493539996</v>
       </c>
       <c r="E12">
-        <v>0.163925862366021</v>
+        <v>0.170889847505064</v>
       </c>
       <c r="F12">
-        <v>0.65147552705692202</v>
+        <v>0.63354023237744095</v>
       </c>
       <c r="G12">
-        <v>0.17929383071866101</v>
+        <v>0.20561281756533101</v>
       </c>
       <c r="H12">
-        <v>0.59766519010704999</v>
+        <v>0.60465116279069697</v>
       </c>
       <c r="I12">
-        <v>0.21163406284080499</v>
+        <v>0.21278789524724701</v>
       </c>
       <c r="J12">
-        <v>0.783056478405315</v>
+        <v>0.71373200442967799</v>
       </c>
       <c r="K12">
-        <v>0.23725611229839999</v>
+        <v>0.26189108854335702</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1247,28 +1247,28 @@
         <v>14</v>
       </c>
       <c r="D13">
-        <v>0.54212809154669594</v>
+        <v>0.56005906238464298</v>
       </c>
       <c r="E13">
-        <v>0.175433337430112</v>
+        <v>0.17772888646138901</v>
       </c>
       <c r="F13">
-        <v>0.57995492879213795</v>
+        <v>0.60012287454147895</v>
       </c>
       <c r="G13">
-        <v>0.180068611832921</v>
+        <v>0.184523009734018</v>
       </c>
       <c r="H13">
-        <v>0.59486895533407103</v>
+        <v>0.61546696197858897</v>
       </c>
       <c r="I13">
-        <v>0.21113493378142401</v>
+        <v>0.22403438801151901</v>
       </c>
       <c r="J13">
-        <v>0.62480620155038702</v>
+        <v>0.65365448504983403</v>
       </c>
       <c r="K13">
-        <v>0.252244176438848</v>
+        <v>0.257885370717297</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1282,28 +1282,28 @@
         <v>12</v>
       </c>
       <c r="D14">
-        <v>0.54214977600636205</v>
+        <v>0.50321206493070803</v>
       </c>
       <c r="E14">
-        <v>0.14222835715062601</v>
+        <v>0.12592780349659999</v>
       </c>
       <c r="F14">
-        <v>0.68913862445571505</v>
+        <v>0.59737706095781995</v>
       </c>
       <c r="G14">
-        <v>0.11908038965445999</v>
+        <v>0.15566445481107299</v>
       </c>
       <c r="H14">
-        <v>0.56096099132706101</v>
+        <v>0.54965087287076497</v>
       </c>
       <c r="I14">
-        <v>0.16475342779052801</v>
+        <v>0.18315408130574801</v>
       </c>
       <c r="J14">
-        <v>0.959972764973124</v>
+        <v>0.732497910250831</v>
       </c>
       <c r="K14">
-        <v>8.4183746472665494E-2</v>
+        <v>0.23929893905441399</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1314,31 +1314,31 @@
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>0.52061810727716296</v>
+        <v>0.48993282196695598</v>
       </c>
       <c r="E15">
-        <v>0.12740025487572099</v>
+        <v>0.109245991665173</v>
       </c>
       <c r="F15">
-        <v>0.62478555179817197</v>
+        <v>0.57565129479086496</v>
       </c>
       <c r="G15">
-        <v>0.12826387040083201</v>
+        <v>0.120215493301918</v>
       </c>
       <c r="H15">
-        <v>0.57207542673324896</v>
+        <v>0.558550311337769</v>
       </c>
       <c r="I15">
-        <v>0.17799275126201899</v>
+        <v>0.16939925414798301</v>
       </c>
       <c r="J15">
-        <v>0.77257598129980698</v>
+        <v>0.67998915869681598</v>
       </c>
       <c r="K15">
-        <v>0.198102236617479</v>
+        <v>0.22737465146083499</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1352,28 +1352,28 @@
         <v>14</v>
       </c>
       <c r="D16">
-        <v>0.51994898148044799</v>
+        <v>0.50713435541013696</v>
       </c>
       <c r="E16">
-        <v>0.11377262980611901</v>
+        <v>0.117043519894471</v>
       </c>
       <c r="F16">
-        <v>0.58416045109428805</v>
+        <v>0.57305227632332301</v>
       </c>
       <c r="G16">
-        <v>0.122993437325586</v>
+        <v>0.12876921024955301</v>
       </c>
       <c r="H16">
-        <v>0.56500832838492099</v>
+        <v>0.55545564117005497</v>
       </c>
       <c r="I16">
-        <v>0.17271525782024699</v>
+        <v>0.180373454910744</v>
       </c>
       <c r="J16">
-        <v>0.64817483509386997</v>
+        <v>0.63470690767245397</v>
       </c>
       <c r="K16">
-        <v>0.15467029938985599</v>
+        <v>0.15087790928327599</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1384,31 +1384,31 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>0.49189635810651899</v>
+        <v>0.48839625165316902</v>
       </c>
       <c r="E17">
-        <v>0.109454694052619</v>
+        <v>0.13553960224365399</v>
       </c>
       <c r="F17">
-        <v>0.57943936591481804</v>
+        <v>0.558228470373344</v>
       </c>
       <c r="G17">
-        <v>0.118422088996333</v>
+        <v>0.14652479902683199</v>
       </c>
       <c r="H17">
-        <v>0.55817669924174995</v>
+        <v>0.55705570898889301</v>
       </c>
       <c r="I17">
-        <v>0.163368642801731</v>
+        <v>0.19422363348147401</v>
       </c>
       <c r="J17">
-        <v>0.68853876935131397</v>
+        <v>0.63463672591188203</v>
       </c>
       <c r="K17">
-        <v>0.22934237641296201</v>
+        <v>0.23008488341646799</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1419,31 +1419,31 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>0.566038721723784</v>
+        <v>0.54999413883503401</v>
       </c>
       <c r="E18">
-        <v>0.174956508001779</v>
+        <v>0.11857857840252101</v>
       </c>
       <c r="F18">
-        <v>0.69488198231069298</v>
+        <v>0.63733349159127195</v>
       </c>
       <c r="G18">
-        <v>0.146638214802433</v>
+        <v>0.13907516449610099</v>
       </c>
       <c r="H18">
-        <v>0.56656753754521005</v>
+        <v>0.57973994504972803</v>
       </c>
       <c r="I18">
-        <v>0.17341446329815399</v>
+        <v>0.18011868870870901</v>
       </c>
       <c r="J18">
-        <v>0.94592501645079996</v>
+        <v>0.76946852937533705</v>
       </c>
       <c r="K18">
-        <v>0.10639292403692301</v>
+        <v>0.190264114862566</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -1454,31 +1454,31 @@
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19">
-        <v>0.56394762720712699</v>
+        <v>0.56437029463165</v>
       </c>
       <c r="E19">
-        <v>0.13522184600414899</v>
+        <v>0.15541335341446399</v>
       </c>
       <c r="F19">
-        <v>0.64944922075239497</v>
+        <v>0.63078524718222295</v>
       </c>
       <c r="G19">
-        <v>0.145482279550675</v>
+        <v>0.17325186747483701</v>
       </c>
       <c r="H19">
-        <v>0.58192638909663696</v>
+        <v>0.57975425613265297</v>
       </c>
       <c r="I19">
-        <v>0.17903042343789499</v>
+        <v>0.18715972527296201</v>
       </c>
       <c r="J19">
-        <v>0.78807318053812703</v>
+        <v>0.74170255037820698</v>
       </c>
       <c r="K19">
-        <v>0.179831010367419</v>
+        <v>0.226892929972799</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1492,28 +1492,28 @@
         <v>13</v>
       </c>
       <c r="D20">
-        <v>0.56287470090034697</v>
+        <v>0.55341447339710204</v>
       </c>
       <c r="E20">
-        <v>0.15631878269265001</v>
+        <v>0.15016859985533901</v>
       </c>
       <c r="F20">
-        <v>0.62523811337426005</v>
+        <v>0.60027507230563404</v>
       </c>
       <c r="G20">
-        <v>0.169770931366031</v>
+        <v>0.17779640521537701</v>
       </c>
       <c r="H20">
-        <v>0.58820598509363498</v>
+        <v>0.58594833590720996</v>
       </c>
       <c r="I20">
-        <v>0.199500016044516</v>
+        <v>0.20624721368563401</v>
       </c>
       <c r="J20">
-        <v>0.71760302242561402</v>
+        <v>0.67708003462150401</v>
       </c>
       <c r="K20">
-        <v>0.20268653789285401</v>
+        <v>0.233618595009428</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1527,28 +1527,28 @@
         <v>14</v>
       </c>
       <c r="D21">
-        <v>0.52994710185583105</v>
+        <v>0.52645731126970896</v>
       </c>
       <c r="E21">
-        <v>0.114187003361301</v>
+        <v>9.6990448140343896E-2</v>
       </c>
       <c r="F21">
-        <v>0.58118216556617996</v>
+        <v>0.57453402203912096</v>
       </c>
       <c r="G21">
-        <v>0.13933213699604699</v>
+        <v>0.130376316589944</v>
       </c>
       <c r="H21">
-        <v>0.589506813853512</v>
+        <v>0.58494575320120701</v>
       </c>
       <c r="I21">
-        <v>0.195581764173271</v>
+        <v>0.18959416398304599</v>
       </c>
       <c r="J21">
-        <v>0.62641983574638205</v>
+        <v>0.61859123024335805</v>
       </c>
       <c r="K21">
-        <v>0.164467553359018</v>
+        <v>0.17054185347123199</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1559,31 +1559,31 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>0.56543421949904704</v>
+        <v>0.55669217279973904</v>
       </c>
       <c r="E22">
-        <v>0.15994301988742399</v>
+        <v>0.138803902382822</v>
       </c>
       <c r="F22">
-        <v>0.69874785290182695</v>
+        <v>0.64881353876081505</v>
       </c>
       <c r="G22">
-        <v>0.13128046406395799</v>
+        <v>0.13438282366128099</v>
       </c>
       <c r="H22">
-        <v>0.56769461483758499</v>
+        <v>0.58877103152231502</v>
       </c>
       <c r="I22">
-        <v>0.16568991749338199</v>
+        <v>0.18116812128152901</v>
       </c>
       <c r="J22">
-        <v>0.95939050409674598</v>
+        <v>0.78830639499087596</v>
       </c>
       <c r="K22">
-        <v>6.8442869711644594E-2</v>
+        <v>0.17651009023304401</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -1594,31 +1594,31 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23">
-        <v>0.55645456550519501</v>
+        <v>0.52654881663925401</v>
       </c>
       <c r="E23">
-        <v>0.14474999893399201</v>
+        <v>0.14893078154011299</v>
       </c>
       <c r="F23">
-        <v>0.65248556180501804</v>
+        <v>0.62179978637649802</v>
       </c>
       <c r="G23">
-        <v>0.13591914421944101</v>
+        <v>0.15049614051855001</v>
       </c>
       <c r="H23">
-        <v>0.58840428605685202</v>
+        <v>0.56200886037956299</v>
       </c>
       <c r="I23">
-        <v>0.184771957419648</v>
+        <v>0.17390702987506801</v>
       </c>
       <c r="J23">
-        <v>0.79909170001278296</v>
+        <v>0.76920599200640905</v>
       </c>
       <c r="K23">
-        <v>0.170256130399846</v>
+        <v>0.20969177998114999</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -1632,28 +1632,28 @@
         <v>13</v>
       </c>
       <c r="D24">
-        <v>0.550741293933799</v>
+        <v>0.54992297392874301</v>
       </c>
       <c r="E24">
-        <v>0.153532386131012</v>
+        <v>0.13225208906115399</v>
       </c>
       <c r="F24">
-        <v>0.62357528454643996</v>
+        <v>0.61791370629112297</v>
       </c>
       <c r="G24">
-        <v>0.15582520224819901</v>
+        <v>0.14080253639180501</v>
       </c>
       <c r="H24">
-        <v>0.58627574324060705</v>
+        <v>0.60974728146230694</v>
       </c>
       <c r="I24">
-        <v>0.19394123355694701</v>
+        <v>0.20545178287243701</v>
       </c>
       <c r="J24">
-        <v>0.72800000474512905</v>
+        <v>0.70666962703650305</v>
       </c>
       <c r="K24">
-        <v>0.204310907658067</v>
+        <v>0.20824310097276999</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -1667,28 +1667,28 @@
         <v>14</v>
       </c>
       <c r="D25">
-        <v>0.52769624969756701</v>
+        <v>0.51727571115334903</v>
       </c>
       <c r="E25">
-        <v>0.14425118793651101</v>
+        <v>0.15508546820307401</v>
       </c>
       <c r="F25">
-        <v>0.59580547572426101</v>
+        <v>0.57823653659471397</v>
       </c>
       <c r="G25">
-        <v>0.15610564500292401</v>
+        <v>0.17358618550520899</v>
       </c>
       <c r="H25">
-        <v>0.56580289565475606</v>
+        <v>0.55016511895876796</v>
       </c>
       <c r="I25">
-        <v>0.18296839235929799</v>
+        <v>0.20603276160607001</v>
       </c>
       <c r="J25">
-        <v>0.678756130933448</v>
+        <v>0.65257230117809495</v>
       </c>
       <c r="K25">
-        <v>0.18385694191201299</v>
+        <v>0.20110979946074301</v>
       </c>
     </row>
   </sheetData>
@@ -1709,72 +1709,72 @@
     <col min="8" max="15" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="26" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D1" s="27" t="s">
+    <row r="1" spans="1:15" s="25" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="M1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="N1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="O1" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31" t="s">
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="31" t="s">
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="33"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="38"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="36"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="10" t="s">
         <v>20</v>
       </c>
@@ -1816,10 +1816,10 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="39" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1827,315 +1827,315 @@
       </c>
       <c r="D4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>52.0618 ± 12.74</v>
-      </c>
-      <c r="E4" s="6" t="str">
+        <v>48.8396 ± 13.55</v>
+      </c>
+      <c r="E4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>62.4786 ± 12.83</v>
+        <v>55.8228 ± 14.65</v>
       </c>
       <c r="F4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>57.2075 ± 17.80</v>
+        <v>55.7056 ± 19.42</v>
       </c>
       <c r="G4" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>77.2576 ± 19.81</v>
+        <v>63.4637 ± 23.01</v>
       </c>
       <c r="H4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>56.3948 ± 13.52</v>
-      </c>
-      <c r="I4" s="7" t="str">
+        <v>54.9994 ± 11.86</v>
+      </c>
+      <c r="I4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>64.9449 ± 14.55</v>
+        <v>63.7333 ± 13.91</v>
       </c>
       <c r="J4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>58.1926 ± 17.90</v>
-      </c>
-      <c r="K4" s="14" t="str">
+        <v>57.9740 ± 18.01</v>
+      </c>
+      <c r="K4" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>78.8073 ± 17.98</v>
-      </c>
-      <c r="L4" s="13" t="str">
+        <v>76.9469 ± 19.03</v>
+      </c>
+      <c r="L4" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>55.6455 ± 14.47</v>
-      </c>
-      <c r="M4" s="7" t="str">
+        <v>55.6692 ± 13.88</v>
+      </c>
+      <c r="M4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>65.2486 ± 13.59</v>
+        <v>64.8814 ± 13.44</v>
       </c>
       <c r="N4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>58.8404 ± 18.48</v>
-      </c>
-      <c r="O4" s="14" t="str">
+        <v>58.8771 ± 18.12</v>
+      </c>
+      <c r="O4" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>79.9092 ± 17.03</v>
+        <v>78.8306 ± 17.65</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>49.1896 ± 10.95</v>
+        <v>48.9933 ± 10.92</v>
       </c>
       <c r="E5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>57.9439 ± 11.84</v>
+        <v>57.5651 ± 12.02</v>
       </c>
       <c r="F5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>55.8177 ± 16.34</v>
+        <v>55.8550 ± 16.94</v>
       </c>
       <c r="G5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>68.8539 ± 22.93</v>
+        <v>67.9989 ± 22.74</v>
       </c>
       <c r="H5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>56.2875 ± 15.63</v>
+        <v>55.3414 ± 15.02</v>
       </c>
       <c r="I5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>62.5238 ± 16.98</v>
-      </c>
-      <c r="J5" s="8" t="str">
+        <v>60.0275 ± 17.78</v>
+      </c>
+      <c r="J5" s="32" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>58.8206 ± 19.95</v>
+        <v>58.5948 ± 20.62</v>
       </c>
       <c r="K5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>71.7603 ± 20.27</v>
+        <v>67.7080 ± 23.36</v>
       </c>
       <c r="L5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>55.0741 ± 15.35</v>
+        <v>54.9923 ± 13.23</v>
       </c>
       <c r="M5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>62.3575 ± 15.58</v>
-      </c>
-      <c r="N5" s="8" t="str">
+        <v>61.7914 ± 14.08</v>
+      </c>
+      <c r="N5" s="32" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>58.6276 ± 19.39</v>
+        <v>60.9747 ± 20.55</v>
       </c>
       <c r="O5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>72.8000 ± 20.43</v>
+        <v>70.6670 ± 20.82</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="18" t="str">
+      <c r="D6" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>54.2150 ± 14.22</v>
-      </c>
-      <c r="E6" s="7" t="str">
+        <v>50.3212 ± 12.59</v>
+      </c>
+      <c r="E6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>68.9139 ± 11.91</v>
-      </c>
-      <c r="F6" s="7" t="str">
+        <v>59.7377 ± 15.57</v>
+      </c>
+      <c r="F6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>56.0961 ± 16.48</v>
+        <v>54.9651 ± 18.32</v>
       </c>
       <c r="G6" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>95.9973 ± 8.42</v>
+        <v>73.2498 ± 23.93</v>
       </c>
       <c r="H6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>56.6039 ± 17.50</v>
-      </c>
-      <c r="I6" s="6" t="str">
+        <v>56.4370 ± 15.54</v>
+      </c>
+      <c r="I6" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>69.4882 ± 14.66</v>
+        <v>63.0785 ± 17.33</v>
       </c>
       <c r="J6" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>56.6568 ± 17.34</v>
-      </c>
-      <c r="K6" s="19" t="str">
+        <v>57.9754 ± 18.72</v>
+      </c>
+      <c r="K6" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>94.5925 ± 10.64</v>
-      </c>
-      <c r="L6" s="18" t="str">
+        <v>74.1703 ± 22.69</v>
+      </c>
+      <c r="L6" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>56.5434 ± 15.99</v>
-      </c>
-      <c r="M6" s="6" t="str">
+        <v>52.6549 ± 14.89</v>
+      </c>
+      <c r="M6" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>69.8748 ± 13.13</v>
+        <v>62.1800 ± 15.05</v>
       </c>
       <c r="N6" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>56.7695 ± 16.57</v>
-      </c>
-      <c r="O6" s="19" t="str">
+        <v>56.2009 ± 17.39</v>
+      </c>
+      <c r="O6" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>95.9391 ± 6.84</v>
+        <v>76.9206 ± 20.97</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="15" t="str">
+      <c r="D7" s="48" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>51.9949 ± 11.38</v>
+        <v>50.7134 ± 11.70</v>
       </c>
       <c r="E7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>58.4160 ± 12.30</v>
-      </c>
-      <c r="F7" s="24" t="str">
+        <v>57.3052 ± 12.88</v>
+      </c>
+      <c r="F7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>56.5008 ± 17.27</v>
+        <v>55.5456 ± 18.04</v>
       </c>
       <c r="G7" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>64.8175 ± 15.47</v>
+        <v>63.4707 ± 15.09</v>
       </c>
       <c r="H7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>52.9947 ± 11.42</v>
+        <v>52.6457 ± 9.70</v>
       </c>
       <c r="I7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>58.1182 ± 13.93</v>
-      </c>
-      <c r="J7" s="24" t="str">
+        <v>57.4534 ± 13.04</v>
+      </c>
+      <c r="J7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>58.9507 ± 19.56</v>
+        <v>58.4946 ± 18.96</v>
       </c>
       <c r="K7" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>62.6420 ± 16.45</v>
+        <v>61.8591 ± 17.05</v>
       </c>
       <c r="L7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>52.7696 ± 14.43</v>
+        <v>51.7276 ± 15.51</v>
       </c>
       <c r="M7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>59.5805 ± 15.61</v>
-      </c>
-      <c r="N7" s="24" t="str">
+        <v>57.8237 ± 17.36</v>
+      </c>
+      <c r="N7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>56.5803 ± 18.30</v>
+        <v>55.0165 ± 20.60</v>
       </c>
       <c r="O7" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>67.8756 ± 18.39</v>
+        <v>65.2572 ± 20.11</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="26"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="1"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28" t="s">
+      <c r="A9" s="25"/>
+      <c r="B9" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="42" t="s">
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="42" t="s">
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="44"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="47"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="46" t="s">
+      <c r="I10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="46" t="s">
+      <c r="J10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="45" t="s">
+      <c r="L10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="46" t="s">
+      <c r="M10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="46" t="s">
+      <c r="N10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="47" t="s">
+      <c r="O10" s="31" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="39" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -2143,222 +2143,222 @@
       </c>
       <c r="D11" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>53.0011 ± 15.93</v>
+        <v>54.0329 ± 18.20</v>
       </c>
       <c r="E11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>61.9005 ± 15.44</v>
+        <v>58.3459 ± 19.75</v>
       </c>
       <c r="F11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>57.1512 ± 18.09</v>
+        <v>57.7824 ± 21.24</v>
       </c>
       <c r="G11" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>74.9723 ± 23.93</v>
+        <v>64.4408 ± 26.35</v>
       </c>
       <c r="H11" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>61.6067 ± 18.40</v>
+        <v>60.7346 ± 18.61</v>
       </c>
       <c r="I11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>68.3272 ± 17.44</v>
-      </c>
-      <c r="J11" s="6" t="str">
+        <v>65.4195 ± 19.23</v>
+      </c>
+      <c r="J11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>62.7556 ± 19.85</v>
+        <v>63.8298 ± 22.24</v>
       </c>
       <c r="K11" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>80.4153 ± 22.15</v>
+        <v>73.3167 ± 24.77</v>
       </c>
       <c r="L11" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>57.3994 ± 16.39</v>
+        <v>57.1410 ± 17.74</v>
       </c>
       <c r="M11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>65.1476 ± 17.93</v>
+        <v>63.8948 ± 19.29</v>
       </c>
       <c r="N11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>59.7665 ± 21.16</v>
-      </c>
-      <c r="O11" s="14" t="str">
+        <v>59.4592 ± 22.05</v>
+      </c>
+      <c r="O11" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>78.3056 ± 23.73</v>
+        <v>74.9723 ± 24.72</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="25" t="str">
+      <c r="D12" s="24" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>58.4330 ± 15.43</v>
+        <v>58.1423 ± 16.22</v>
       </c>
       <c r="E12" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>65.5761 ± 14.31</v>
-      </c>
-      <c r="F12" s="48" t="str">
+        <v>64.8592 ± 15.43</v>
+      </c>
+      <c r="F12" s="32" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>61.4812 ± 17.11</v>
+        <v>60.6478 ± 17.74</v>
       </c>
       <c r="G12" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>75.3156 ± 20.09</v>
-      </c>
-      <c r="H12" s="25" t="str">
+        <v>74.5847 ± 21.28</v>
+      </c>
+      <c r="H12" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>62.7159 ± 15.46</v>
+        <v>64.6142 ± 18.51</v>
       </c>
       <c r="I12" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>66.4188 ± 18.29</v>
-      </c>
-      <c r="J12" s="8" t="str">
+        <v>64.3142 ± 23.58</v>
+      </c>
+      <c r="J12" s="32" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>64.7841 ± 20.47</v>
+        <v>68.7320 ± 25.00</v>
       </c>
       <c r="K12" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>73.8594 ± 24.51</v>
-      </c>
-      <c r="L12" s="25" t="str">
+        <v>66.9823 ± 28.70</v>
+      </c>
+      <c r="L12" s="24" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>63.3093 ± 17.47</v>
-      </c>
-      <c r="M12" s="48" t="str">
+        <v>63.4718 ± 16.40</v>
+      </c>
+      <c r="M12" s="32" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>68.3265 ± 17.27</v>
-      </c>
-      <c r="N12" s="48" t="str">
+        <v>65.5777 ± 19.88</v>
+      </c>
+      <c r="N12" s="32" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>64.8948 ± 18.66</v>
+        <v>65.7032 ± 20.69</v>
       </c>
       <c r="O12" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>76.8494 ± 22.46</v>
+        <v>69.9280 ± 24.89</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="34"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>57.7076 ± 14.40</v>
+        <v>57.8802 ± 18.49</v>
       </c>
       <c r="E13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>69.7383 ± 11.38</v>
+        <v>64.8732 ± 16.76</v>
       </c>
       <c r="F13" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>58.7135 ± 15.84</v>
+        <v>60.2796 ± 17.35</v>
       </c>
       <c r="G13" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>91.3732 ± 13.00</v>
-      </c>
-      <c r="H13" s="13" t="str">
+        <v>75.0111 ± 21.94</v>
+      </c>
+      <c r="H13" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>59.8828 ± 15.76</v>
+        <v>64.9354 ± 19.20</v>
       </c>
       <c r="I13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>69.5589 ± 13.94</v>
+        <v>68.8011 ± 18.88</v>
       </c>
       <c r="J13" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>60.7004 ± 16.70</v>
+        <v>68.2835 ± 22.07</v>
       </c>
       <c r="K13" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>86.4729 ± 17.54</v>
+        <v>74.0642 ± 23.14</v>
       </c>
       <c r="L13" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>58.6074 ± 12.60</v>
+        <v>59.0633 ± 17.09</v>
       </c>
       <c r="M13" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>68.2018 ± 12.64</v>
+        <v>63.3540 ± 20.56</v>
       </c>
       <c r="N13" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>59.6862 ± 16.27</v>
-      </c>
-      <c r="O13" s="19" t="str">
+        <v>60.4651 ± 21.28</v>
+      </c>
+      <c r="O13" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>84.9280 ± 18.34</v>
+        <v>71.3732 ± 26.19</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="35"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="21" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>48.5640 ± 18.99</v>
+        <v>52.7621 ± 18.51</v>
       </c>
       <c r="E14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>52.8251 ± 20.35</v>
+        <v>56.2333 ± 18.72</v>
       </c>
       <c r="F14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>54.5155 ± 22.31</v>
+        <v>59.0338 ± 22.65</v>
       </c>
       <c r="G14" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>57.2259 ± 27.10</v>
+        <v>58.4662 ± 22.88</v>
       </c>
       <c r="H14" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>53.3684 ± 18.85</v>
+        <v>55.1458 ± 16.38</v>
       </c>
       <c r="I14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>54.8034 ± 22.75</v>
+        <v>57.0601 ± 18.27</v>
       </c>
       <c r="J14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>54.9723 ± 23.87</v>
+        <v>59.2027 ± 19.78</v>
       </c>
       <c r="K14" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>57.6800 ± 26.29</v>
+        <v>59.8837 ± 25.53</v>
       </c>
       <c r="L14" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>54.2128 ± 17.54</v>
+        <v>56.0059 ± 17.77</v>
       </c>
       <c r="M14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>57.9955 ± 18.01</v>
+        <v>60.0123 ± 18.45</v>
       </c>
       <c r="N14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>59.4869 ± 21.11</v>
+        <v>61.5467 ± 22.40</v>
       </c>
       <c r="O14" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>62.4806 ± 25.22</v>
+        <v>65.3654 ± 25.79</v>
       </c>
     </row>
   </sheetData>
